--- a/artfynd/S 127-2026 artfynd.xlsx
+++ b/artfynd/S 127-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119226106</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127945291</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119226287</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119225979</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268241</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,6 +1409,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119367540</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,6 +1530,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127945499</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1602,6 +1642,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258859</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1704,6 +1749,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560208</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1816,6 +1866,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119369329</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1931,6 +1986,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119225230</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2050,6 +2110,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119225373</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2166,6 +2231,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258141</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2287,6 +2357,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119367600</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2403,6 +2478,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119367667</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2510,6 +2590,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119519054</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2621,6 +2706,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119519931</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2728,6 +2818,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119764988</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2835,6 +2930,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119765573</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2944,6 +3044,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119905244</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3050,6 +3155,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560193</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3157,6 +3267,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127945522</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3273,6 +3388,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128665166</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3384,6 +3504,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119225749</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3500,6 +3625,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119225871</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3607,6 +3737,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258145</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3714,6 +3849,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128662232</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3821,6 +3961,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128662652</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3960,6 +4105,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268278</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4099,6 +4249,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268281</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4238,6 +4393,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119268297</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4345,6 +4505,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119368558</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4452,6 +4617,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119368675</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4564,6 +4734,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127945582</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4676,6 +4851,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127946779</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4785,6 +4965,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119905347</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4897,6 +5082,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258774</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5012,6 +5202,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119258953</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5124,6 +5319,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126199420</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5240,6 +5440,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119765224</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5352,6 +5557,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119225708</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5459,6 +5669,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119226493</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5575,6 +5790,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119369208</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5695,6 +5915,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119225651</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5798,6 +6023,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119226499</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5901,8 +6131,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119369098</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>